--- a/keycloak-extension/src/main/resources/template/template.xlsx
+++ b/keycloak-extension/src/main/resources/template/template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rossiiskaia.kv\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\domru-sso\keycloak-extension\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50ABFDC4-C4D2-4B9F-A56B-D096C6B4156B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12420"/>
+    <workbookView xWindow="4395" yWindow="2310" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -20,12 +21,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Небогатикова Ксения Витальевна</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -50,7 +51,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -76,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -114,7 +115,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -140,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -166,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -195,7 +196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -285,7 +286,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -378,23 +379,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Domru.ru" xfId="2"/>
+    <cellStyle name="Domru.ru" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -671,38 +673,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="6" customWidth="1"/>
+    <col min="4" max="5" width="26" style="6" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="30.28515625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -713,7 +716,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Лист1!$A$1:$A$4</xm:f>
           </x14:formula1>
@@ -726,7 +729,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/keycloak-extension/src/main/resources/template/template.xlsx
+++ b/keycloak-extension/src/main/resources/template/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\domru-sso\keycloak-extension\src\main\resources\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Petrov\Java\sso\keycloak-extension\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50ABFDC4-C4D2-4B9F-A56B-D096C6B4156B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8770E534-2191-413D-A9D1-B1ECAC4CDC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4395" yWindow="2310" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -287,7 +287,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -355,6 +355,12 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Open Sans"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -379,7 +385,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -392,6 +398,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Domru.ru" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -674,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" style="6" bestFit="1" customWidth="1"/>
@@ -708,6 +715,9 @@
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="D2" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
